--- a/data/trans_orig/P1421-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P1421-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de migrañas en 2007</t>
+          <t>Población con diagnóstico de migrañas/ jaquecas / cefaleas crónicas / dolor de cabeza frecuente en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5817</t>
+          <t>5185</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19174</t>
+          <t>19027</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9250</t>
+          <t>9921</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24422</t>
+          <t>25107</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17937</t>
+          <t>17684</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>38926</t>
+          <t>39427</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,85%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>674838</t>
+          <t>674985</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>688195</t>
+          <t>688827</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>663929</t>
+          <t>663244</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>679101</t>
+          <t>678430</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1343437</t>
+          <t>1342936</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1364426</t>
+          <t>1364679</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,72%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16245</t>
+          <t>15607</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>35913</t>
+          <t>35508</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>37682</t>
+          <t>37291</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>64946</t>
+          <t>65752</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>59290</t>
+          <t>58585</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>94716</t>
+          <t>94311</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,89%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>925887</t>
+          <t>926292</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>945555</t>
+          <t>946193</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>903447</t>
+          <t>902641</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>930711</t>
+          <t>931102</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>93,21%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1835477</t>
+          <t>1835882</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1870903</t>
+          <t>1871608</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>96,96%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7716</t>
+          <t>7574</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22595</t>
+          <t>22749</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>35068</t>
+          <t>33897</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>62063</t>
+          <t>59395</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>46155</t>
+          <t>48225</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>77098</t>
+          <t>78329</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,75%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>655914</t>
+          <t>655760</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>670793</t>
+          <t>670935</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>621778</t>
+          <t>624446</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>648773</t>
+          <t>649944</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,92%</t>
+          <t>91,31%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1285252</t>
+          <t>1284021</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1316195</t>
+          <t>1314125</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,46%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20504</t>
+          <t>20031</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>39495</t>
+          <t>41157</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>66693</t>
+          <t>67689</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>102642</t>
+          <t>101459</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>94532</t>
+          <t>91635</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>133311</t>
+          <t>134747</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,8%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>902727</t>
+          <t>901065</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>921718</t>
+          <t>922191</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>935970</t>
+          <t>937153</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>971919</t>
+          <t>970923</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,12%</t>
+          <t>90,23%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>93,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1847523</t>
+          <t>1846087</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1886302</t>
+          <t>1889199</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>93,2%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,37%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>62180</t>
+          <t>62800</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>97126</t>
+          <t>98230</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>168059</t>
+          <t>170511</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>221885</t>
+          <t>224671</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>242222</t>
+          <t>243028</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>307169</t>
+          <t>305286</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,59%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3179417</t>
+          <t>3178313</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3214363</t>
+          <t>3213743</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3157312</t>
+          <t>3154526</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3211138</t>
+          <t>3208686</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>93,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6348572</t>
+          <t>6350455</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6413519</t>
+          <t>6412713</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,35%</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de migrañas en 2012</t>
+          <t>Población con diagnóstico de migrañas/ jaquecas / cefaleas crónicas / dolor de cabeza frecuente en 2012 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2832</t>
+          <t>3063</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13153</t>
+          <t>14349</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>36908</t>
+          <t>36247</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>66254</t>
+          <t>66070</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>42693</t>
+          <t>43081</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>74462</t>
+          <t>74162</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,3%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>690316</t>
+          <t>689120</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>700637</t>
+          <t>700406</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>630796</t>
+          <t>630980</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>660142</t>
+          <t>660803</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,5%</t>
+          <t>90,52%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1326057</t>
+          <t>1326357</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1357826</t>
+          <t>1357438</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,7%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,92%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5307</t>
+          <t>5261</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19054</t>
+          <t>18572</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3043,7 +3043,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>35271</t>
+          <t>36441</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>63317</t>
+          <t>64699</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>44824</t>
+          <t>46594</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>74646</t>
+          <t>75663</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,7%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>998893</t>
+          <t>999375</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1012640</t>
+          <t>1012686</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,7 +3151,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>965656</t>
+          <t>964274</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>993702</t>
+          <t>992532</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1972275</t>
+          <t>1971258</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2002097</t>
+          <t>2000327</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,72%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3124</t>
+          <t>3075</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17815</t>
+          <t>16258</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>28240</t>
+          <t>28200</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>54564</t>
+          <t>55604</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3421,7 +3421,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>34811</t>
+          <t>34841</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>64301</t>
+          <t>64769</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3456,7 +3456,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,22%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>739808</t>
+          <t>741365</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>754499</t>
+          <t>754548</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,7 +3494,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>722610</t>
+          <t>721570</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>748934</t>
+          <t>748974</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,7 +3529,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1470496</t>
+          <t>1470028</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1499986</t>
+          <t>1499956</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9307</t>
+          <t>9158</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24259</t>
+          <t>24643</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>39264</t>
+          <t>39529</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>67247</t>
+          <t>68005</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>52874</t>
+          <t>52358</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>85392</t>
+          <t>85802</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,29%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>922450</t>
+          <t>922066</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>937402</t>
+          <t>937551</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>984654</t>
+          <t>983896</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1012637</t>
+          <t>1012372</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>93,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1913218</t>
+          <t>1912808</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1945736</t>
+          <t>1946252</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,38%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>30269</t>
+          <t>30012</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>56895</t>
+          <t>55803</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4072,7 +4072,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>164439</t>
+          <t>166549</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>218165</t>
+          <t>217776</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>200918</t>
+          <t>202730</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>263521</t>
+          <t>263268</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,7 +4137,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3368853</t>
+          <t>3369945</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3395479</t>
+          <t>3395736</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,7 +4180,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3336933</t>
+          <t>3337322</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3390659</t>
+          <t>3388549</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6717326</t>
+          <t>6717579</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6779929</t>
+          <t>6778117</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4255,7 +4255,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,1%</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de migrañas en 2016</t>
+          <t>Población con diagnóstico de migrañas/ jaquecas / cefaleas crónicas / dolor de cabeza frecuente en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6230</t>
+          <t>6148</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20597</t>
+          <t>19668</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>22704</t>
+          <t>22359</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>44603</t>
+          <t>43098</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>32716</t>
+          <t>32464</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>60849</t>
+          <t>58450</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,34%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>654203</t>
+          <t>655132</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>668570</t>
+          <t>668652</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>628236</t>
+          <t>629741</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>650135</t>
+          <t>650480</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>93,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1286790</t>
+          <t>1289189</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1314923</t>
+          <t>1315175</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,59%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4937</t>
+          <t>4931</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18267</t>
+          <t>18291</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>46899</t>
+          <t>46980</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>80196</t>
+          <t>78745</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5025,7 +5025,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>55464</t>
+          <t>55498</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>90093</t>
+          <t>89607</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5060,7 +5060,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,34%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1004164</t>
+          <t>1004140</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1017494</t>
+          <t>1017500</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>962717</t>
+          <t>964168</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>996014</t>
+          <t>995933</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,7 +5133,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>92,45%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1975251</t>
+          <t>1975737</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2009880</t>
+          <t>2009846</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,7 +5168,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5788</t>
+          <t>5134</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20174</t>
+          <t>20145</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>26404</t>
+          <t>26630</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>51166</t>
+          <t>50932</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>37061</t>
+          <t>36888</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>64253</t>
+          <t>64125</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,15%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>739378</t>
+          <t>739407</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>753764</t>
+          <t>754418</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>733845</t>
+          <t>734079</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>758607</t>
+          <t>758381</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1480310</t>
+          <t>1480438</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1507502</t>
+          <t>1507675</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,61%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9292</t>
+          <t>8852</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24850</t>
+          <t>24316</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>48681</t>
+          <t>48126</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>82069</t>
+          <t>81368</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>62267</t>
+          <t>61237</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>99028</t>
+          <t>99537</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,02%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>912717</t>
+          <t>913251</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>928275</t>
+          <t>928715</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>961710</t>
+          <t>962411</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>995098</t>
+          <t>995653</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,14%</t>
+          <t>92,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1882318</t>
+          <t>1881809</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1919079</t>
+          <t>1920109</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,91%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>35744</t>
+          <t>35392</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>62504</t>
+          <t>62858</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>165825</t>
+          <t>169038</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>221531</t>
+          <t>225855</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>209681</t>
+          <t>211957</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>274692</t>
+          <t>280336</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,04%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3331846</t>
+          <t>3331492</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3358606</t>
+          <t>3358958</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3323011</t>
+          <t>3318687</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3378717</t>
+          <t>3375504</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6664200</t>
+          <t>6658556</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6729211</t>
+          <t>6726935</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>96,95%</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de migrañas en 2023</t>
+          <t>Población con diagnóstico de migrañas/ jaquecas / cefaleas crónicas / dolor de cabeza frecuente en 2023 (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21252</t>
+          <t>20780</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>41967</t>
+          <t>40981</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>50957</t>
+          <t>52290</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>75609</t>
+          <t>75534</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>77416</t>
+          <t>78282</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>111076</t>
+          <t>109627</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,36%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>593474</t>
+          <t>594460</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>614189</t>
+          <t>614661</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>93,55%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>599761</t>
+          <t>599836</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>624413</t>
+          <t>623080</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,8%</t>
+          <t>88,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>92,26%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1199735</t>
+          <t>1201184</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1233395</t>
+          <t>1232529</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>94,03%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>20002</t>
+          <t>16712</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>54030</t>
+          <t>54759</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>76943</t>
+          <t>77789</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>106917</t>
+          <t>107705</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>82927</t>
+          <t>86343</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>154805</t>
+          <t>156158</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,26%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1138834</t>
+          <t>1138105</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1172862</t>
+          <t>1176152</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>849816</t>
+          <t>849028</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>879790</t>
+          <t>878944</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,82%</t>
+          <t>88,74%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1994792</t>
+          <t>1993439</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2066670</t>
+          <t>2063254</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,74%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>95,98%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>22501</t>
+          <t>22289</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>45994</t>
+          <t>45292</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>47942</t>
+          <t>54291</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>132408</t>
+          <t>131024</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>81823</t>
+          <t>82921</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>159288</t>
+          <t>161129</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,86%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>656971</t>
+          <t>657673</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>680464</t>
+          <t>680676</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,46%</t>
+          <t>93,56%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>799343</t>
+          <t>800727</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>883809</t>
+          <t>877460</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,79%</t>
+          <t>85,94%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,17%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1475428</t>
+          <t>1473587</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1552893</t>
+          <t>1551795</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,26%</t>
+          <t>90,14%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>94,93%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>36721</t>
+          <t>39617</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>72012</t>
+          <t>74841</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,82 +7618,82 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
+          <t>8,09%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>134418</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>108348</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>159317</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>12,32%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>9,93%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>14,6%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>244</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>187484</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>156875</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>217140</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>9,3%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
           <t>7,78%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>194</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>134418</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>107374</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>160150</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>12,32%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>9,84%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>14,68%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>244</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>187484</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>158045</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>217713</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>9,3%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>7,84%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,77%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>853598</t>
+          <t>850769</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>888889</t>
+          <t>885993</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,82 +7731,82 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
+          <t>91,91%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>95,72%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>1365</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>956896</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>931997</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>982966</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>87,68%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>85,4%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>90,07%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>2319</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>1829440</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>1799784</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>1860049</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>90,7%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>89,23%</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
           <t>92,22%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>96,03%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1365</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>956896</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>931164</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>983940</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>87,68%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>85,32%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>90,16%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>2319</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>1829440</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>1799211</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>1858879</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>90,7%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>89,21%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>92,16%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>116210</t>
+          <t>115766</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>183145</t>
+          <t>182537</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>324136</t>
+          <t>325032</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>430274</t>
+          <t>430155</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,7 +7996,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>468767</t>
+          <t>470235</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>596982</t>
+          <t>597952</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,41%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3273735</t>
+          <t>3274343</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3340670</t>
+          <t>3341114</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3224894</t>
+          <t>3225013</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3331032</t>
+          <t>3330136</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8114,7 +8114,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,13%</t>
+          <t>91,11%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6515066</t>
+          <t>6514096</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6643281</t>
+          <t>6641813</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,61%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>93,39%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1421-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P1421-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5185</t>
+          <t>5653</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19027</t>
+          <t>19495</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9921</t>
+          <t>9164</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>25107</t>
+          <t>26114</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17684</t>
+          <t>18834</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>39427</t>
+          <t>38426</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,78%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>674985</t>
+          <t>674517</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>688827</t>
+          <t>688359</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>663244</t>
+          <t>662237</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>678430</t>
+          <t>679187</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1342936</t>
+          <t>1343937</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1364679</t>
+          <t>1363529</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,64%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15607</t>
+          <t>15090</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>35508</t>
+          <t>36771</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>37291</t>
+          <t>38140</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>65752</t>
+          <t>65917</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>58585</t>
+          <t>59135</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>94311</t>
+          <t>95340</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,94%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>926292</t>
+          <t>925029</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>946193</t>
+          <t>946710</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>902641</t>
+          <t>902476</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>931102</t>
+          <t>930253</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1835882</t>
+          <t>1834853</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1871608</t>
+          <t>1871058</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>96,94%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7574</t>
+          <t>8392</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22749</t>
+          <t>24295</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>33897</t>
+          <t>34494</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>59395</t>
+          <t>59420</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>48225</t>
+          <t>46714</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>78329</t>
+          <t>78211</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,74%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>655760</t>
+          <t>654214</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>670935</t>
+          <t>670117</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>624446</t>
+          <t>624421</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>649944</t>
+          <t>649347</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1587,7 +1587,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1284021</t>
+          <t>1284139</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1314125</t>
+          <t>1315636</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,57%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20031</t>
+          <t>19915</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>41157</t>
+          <t>40845</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>67689</t>
+          <t>65753</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>101459</t>
+          <t>100851</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>91635</t>
+          <t>92812</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>134747</t>
+          <t>134060</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,77%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>901065</t>
+          <t>901377</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>922191</t>
+          <t>922307</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>937153</t>
+          <t>937761</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>970923</t>
+          <t>972859</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,23%</t>
+          <t>90,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1846087</t>
+          <t>1846774</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1889199</t>
+          <t>1888022</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,31%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>62800</t>
+          <t>63733</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>98230</t>
+          <t>98843</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>170511</t>
+          <t>168324</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>224671</t>
+          <t>222270</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>243028</t>
+          <t>241953</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>305286</t>
+          <t>304359</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,57%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3178313</t>
+          <t>3177700</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3213743</t>
+          <t>3212810</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3154526</t>
+          <t>3156927</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3208686</t>
+          <t>3210873</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>93,42%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6350455</t>
+          <t>6351382</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6412713</t>
+          <t>6413788</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,36%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3063</t>
+          <t>2958</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14349</t>
+          <t>14133</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>36247</t>
+          <t>37026</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>66070</t>
+          <t>65130</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>43081</t>
+          <t>41924</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>74162</t>
+          <t>73505</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,25%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>689120</t>
+          <t>689336</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>700406</t>
+          <t>700511</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,58%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>630980</t>
+          <t>631920</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>660803</t>
+          <t>660024</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,52%</t>
+          <t>90,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1326357</t>
+          <t>1327014</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1357438</t>
+          <t>1358595</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>97,01%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5261</t>
+          <t>5431</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18572</t>
+          <t>19141</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>36441</t>
+          <t>36606</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>64699</t>
+          <t>64148</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>46594</t>
+          <t>44784</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>75663</t>
+          <t>75185</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,67%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>999375</t>
+          <t>998806</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1012686</t>
+          <t>1012516</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>964274</t>
+          <t>964825</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>992532</t>
+          <t>992367</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>93,77%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1971258</t>
+          <t>1971736</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2000327</t>
+          <t>2002137</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,81%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3075</t>
+          <t>3840</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16258</t>
+          <t>16857</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>28200</t>
+          <t>28108</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>55604</t>
+          <t>55389</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>34841</t>
+          <t>34152</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>64769</t>
+          <t>65222</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,25%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>741365</t>
+          <t>740766</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>754548</t>
+          <t>753783</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,49%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>721570</t>
+          <t>721785</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>748974</t>
+          <t>749066</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1470028</t>
+          <t>1469575</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1499956</t>
+          <t>1500645</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,77%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9158</t>
+          <t>9163</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24643</t>
+          <t>25619</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3729,77 +3729,77 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
+          <t>2,71%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>51560</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>39103</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>66087</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>4,9%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>3,72%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>6,28%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>67279</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>51933</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>84452</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>3,37%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
           <t>2,6%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>51560</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>39529</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>68005</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>4,9%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>3,76%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>6,46%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>67279</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>52358</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>85802</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>3,37%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>2,62%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,23%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>922066</t>
+          <t>921090</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>937551</t>
+          <t>937546</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,82 +3837,82 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
+          <t>97,29%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,03%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>952</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>1000341</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>985814</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>1012798</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>95,1%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>93,72%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>96,28%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>1845</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>1931331</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>1914158</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>1946677</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>96,63%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>95,77%</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
           <t>97,4%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>99,03%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>952</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>1000341</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>983896</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>1012372</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>95,1%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>93,54%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>96,24%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1845</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>1931331</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>1912808</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>1946252</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>96,63%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>95,71%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>97,38%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>30012</t>
+          <t>30091</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>55803</t>
+          <t>56183</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4072,7 +4072,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>166549</t>
+          <t>162510</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>217776</t>
+          <t>218997</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>202730</t>
+          <t>201953</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>263268</t>
+          <t>262877</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,7 +4137,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3369945</t>
+          <t>3369565</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3395736</t>
+          <t>3395657</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,7 +4180,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3337322</t>
+          <t>3336101</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3388549</t>
+          <t>3392588</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>93,84%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6717579</t>
+          <t>6717970</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6778117</t>
+          <t>6778894</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4255,7 +4255,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,11%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6148</t>
+          <t>6005</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19668</t>
+          <t>21744</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>22359</t>
+          <t>21192</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>43098</t>
+          <t>43723</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>32464</t>
+          <t>31731</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>58450</t>
+          <t>58729</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,36%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>655132</t>
+          <t>653056</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>668652</t>
+          <t>668795</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>629741</t>
+          <t>629116</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>650480</t>
+          <t>651647</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>93,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1289189</t>
+          <t>1288910</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1315175</t>
+          <t>1315908</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,65%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4931</t>
+          <t>4861</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18291</t>
+          <t>17413</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4990,7 +4990,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>46980</t>
+          <t>45126</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>78745</t>
+          <t>77385</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>55498</t>
+          <t>54749</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>89607</t>
+          <t>89451</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,33%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1004140</t>
+          <t>1005018</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1017500</t>
+          <t>1017570</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,7 +5098,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>964168</t>
+          <t>965528</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>995933</t>
+          <t>997787</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1975737</t>
+          <t>1975893</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2009846</t>
+          <t>2010595</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,35%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5134</t>
+          <t>5173</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20145</t>
+          <t>19811</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5333,7 +5333,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>26630</t>
+          <t>27512</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>50932</t>
+          <t>51752</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>36888</t>
+          <t>37185</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>64125</t>
+          <t>65557</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,24%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>739407</t>
+          <t>739741</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>754418</t>
+          <t>754379</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,7 +5441,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>734079</t>
+          <t>733259</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>758381</t>
+          <t>757499</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1480438</t>
+          <t>1479006</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1507675</t>
+          <t>1507378</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,59%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8852</t>
+          <t>8805</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24316</t>
+          <t>24241</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>48126</t>
+          <t>48116</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>81368</t>
+          <t>80918</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>61237</t>
+          <t>61550</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>99537</t>
+          <t>98681</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,98%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>913251</t>
+          <t>913326</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>928715</t>
+          <t>928762</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>962411</t>
+          <t>962861</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>995653</t>
+          <t>995663</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,7 +5819,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,2%</t>
+          <t>92,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1881809</t>
+          <t>1882665</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1920109</t>
+          <t>1919796</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,89%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>35392</t>
+          <t>35615</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>62858</t>
+          <t>64238</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>169038</t>
+          <t>166148</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>225855</t>
+          <t>223414</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>211957</t>
+          <t>212211</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>280336</t>
+          <t>273862</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,95%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3331492</t>
+          <t>3330112</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3358958</t>
+          <t>3358735</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3318687</t>
+          <t>3321128</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3375504</t>
+          <t>3378394</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,7%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6658556</t>
+          <t>6665030</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6726935</t>
+          <t>6726681</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,94%</t>
         </is>
       </c>
     </row>
@@ -6569,32 +6569,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>29755</t>
+          <t>30945</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>20780</t>
+          <t>22131</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>40981</t>
+          <t>43520</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6604,32 +6604,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>62902</t>
+          <t>67581</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>52290</t>
+          <t>55411</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>75534</t>
+          <t>83196</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>92656</t>
+          <t>98526</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>78282</t>
+          <t>84485</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>109627</t>
+          <t>120191</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,44%</t>
         </is>
       </c>
     </row>
@@ -6682,32 +6682,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>605686</t>
+          <t>659765</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>594460</t>
+          <t>647190</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>614661</t>
+          <t>668579</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>93,7%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6717,32 +6717,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>612468</t>
+          <t>665141</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>599836</t>
+          <t>649526</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>623080</t>
+          <t>677311</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>90,78%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,82%</t>
+          <t>88,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>92,44%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1218155</t>
+          <t>1324905</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1201184</t>
+          <t>1303240</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1232529</t>
+          <t>1338946</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>93,08%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>91,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>94,06%</t>
         </is>
       </c>
     </row>
@@ -6795,17 +6795,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6830,17 +6830,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>675370</t>
+          <t>732722</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>675370</t>
+          <t>732722</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>675370</t>
+          <t>732722</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1310811</t>
+          <t>1423431</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1310811</t>
+          <t>1423431</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1310811</t>
+          <t>1423431</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6912,32 +6912,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>37112</t>
+          <t>39784</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16712</t>
+          <t>28201</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>54759</t>
+          <t>57210</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6947,32 +6947,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>91818</t>
+          <t>103792</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>77789</t>
+          <t>87392</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>107705</t>
+          <t>120571</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>128931</t>
+          <t>143577</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>86343</t>
+          <t>123851</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>156158</t>
+          <t>165627</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,82%</t>
         </is>
       </c>
     </row>
@@ -7025,32 +7025,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1155752</t>
+          <t>1009133</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1138105</t>
+          <t>991707</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1176152</t>
+          <t>1020716</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>94,55%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7060,32 +7060,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>864915</t>
+          <t>965649</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>849028</t>
+          <t>948870</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>878944</t>
+          <t>982049</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>90,4%</t>
+          <t>90,29%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,74%</t>
+          <t>88,73%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>91,83%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>2020666</t>
+          <t>1974781</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1993439</t>
+          <t>1952731</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2063254</t>
+          <t>1994507</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>93,22%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>92,18%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>94,15%</t>
         </is>
       </c>
     </row>
@@ -7138,17 +7138,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7173,17 +7173,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>956733</t>
+          <t>1069441</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>956733</t>
+          <t>1069441</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>956733</t>
+          <t>1069441</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2149597</t>
+          <t>2118358</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2149597</t>
+          <t>2118358</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2149597</t>
+          <t>2118358</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>32769</t>
+          <t>36389</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>22289</t>
+          <t>26026</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>45292</t>
+          <t>50186</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>96987</t>
+          <t>109451</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>54291</t>
+          <t>92191</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>131024</t>
+          <t>127352</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>129756</t>
+          <t>145840</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>82921</t>
+          <t>124708</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>161129</t>
+          <t>165427</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>10,27%</t>
         </is>
       </c>
     </row>
@@ -7368,32 +7368,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>670196</t>
+          <t>764828</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>657673</t>
+          <t>751031</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>680676</t>
+          <t>775191</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7403,32 +7403,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>834764</t>
+          <t>700637</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>800727</t>
+          <t>682736</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>877460</t>
+          <t>717897</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>89,59%</t>
+          <t>86,49%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,94%</t>
+          <t>84,28%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>88,62%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1504960</t>
+          <t>1465465</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1473587</t>
+          <t>1445878</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1551795</t>
+          <t>1486597</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>90,95%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,14%</t>
+          <t>89,73%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>92,26%</t>
         </is>
       </c>
     </row>
@@ -7481,17 +7481,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>702965</t>
+          <t>801217</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>702965</t>
+          <t>801217</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>702965</t>
+          <t>801217</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7516,17 +7516,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>931751</t>
+          <t>810088</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>931751</t>
+          <t>810088</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>931751</t>
+          <t>810088</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1634716</t>
+          <t>1611305</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1634716</t>
+          <t>1611305</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1634716</t>
+          <t>1611305</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7598,32 +7598,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>53066</t>
+          <t>53144</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>39617</t>
+          <t>39896</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>74841</t>
+          <t>74887</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7633,32 +7633,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>134418</t>
+          <t>141631</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>108348</t>
+          <t>123123</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>159317</t>
+          <t>166329</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>187484</t>
+          <t>194775</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>156875</t>
+          <t>172991</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>217140</t>
+          <t>222757</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,59%</t>
         </is>
       </c>
     </row>
@@ -7711,32 +7711,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>872544</t>
+          <t>934085</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>850769</t>
+          <t>912342</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>885993</t>
+          <t>947333</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>92,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>956896</t>
+          <t>975356</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>931997</t>
+          <t>950658</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>982966</t>
+          <t>993864</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>87,68%</t>
+          <t>87,32%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,4%</t>
+          <t>85,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,07%</t>
+          <t>88,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1829440</t>
+          <t>1909441</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1799784</t>
+          <t>1881459</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1860049</t>
+          <t>1931225</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>90,7%</t>
+          <t>90,74%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,23%</t>
+          <t>89,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,22%</t>
+          <t>91,78%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>925610</t>
+          <t>987229</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>925610</t>
+          <t>987229</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>925610</t>
+          <t>987229</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1091314</t>
+          <t>1116987</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1091314</t>
+          <t>1116987</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1091314</t>
+          <t>1116987</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2016924</t>
+          <t>2104216</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2016924</t>
+          <t>2104216</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2016924</t>
+          <t>2104216</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7941,32 +7941,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>152702</t>
+          <t>160263</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>115766</t>
+          <t>133411</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>182537</t>
+          <t>188991</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7976,32 +7976,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>386125</t>
+          <t>422455</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>325032</t>
+          <t>389366</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>430155</t>
+          <t>457124</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>538827</t>
+          <t>582717</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>470235</t>
+          <t>545152</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>597952</t>
+          <t>628725</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,66%</t>
         </is>
       </c>
     </row>
@@ -8054,32 +8054,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3304178</t>
+          <t>3367810</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3274343</t>
+          <t>3339082</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3341114</t>
+          <t>3394662</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8089,32 +8089,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3269043</t>
+          <t>3306783</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3225013</t>
+          <t>3272114</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3330136</t>
+          <t>3339872</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>89,44%</t>
+          <t>88,67%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,23%</t>
+          <t>87,74%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>89,56%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>6573221</t>
+          <t>6674593</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6514096</t>
+          <t>6628585</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6641813</t>
+          <t>6712158</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>91,97%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>91,34%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>92,49%</t>
         </is>
       </c>
     </row>
@@ -8167,17 +8167,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3456880</t>
+          <t>3528073</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3456880</t>
+          <t>3528073</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3456880</t>
+          <t>3528073</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8202,17 +8202,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3655168</t>
+          <t>3729238</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3655168</t>
+          <t>3729238</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3655168</t>
+          <t>3729238</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7112048</t>
+          <t>7257310</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7112048</t>
+          <t>7257310</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7112048</t>
+          <t>7257310</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
